--- a/backend/backups/category12_technology_digital_services_FINAL.xlsx
+++ b/backend/backups/category12_technology_digital_services_FINAL.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ALL_SERVICES_FINAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,24 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,18 +46,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -74,8 +57,8 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,115 +425,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>service_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>service_name</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>subcategory</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>subcategory</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>base_price</t>
+          <t>price</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>distinct_features_json</t>
+          <t>highlights</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggested_addons_json</t>
+          <t>included</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>faqs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>warranty</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d4e6bfe2-ecbd-5815-b7c7-05784074772a</t>
+          <t>2e15793f-1ce5-5cda-88eb-72fb5eedece4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair Service Variation 1</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Computer &amp; Device Support</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair</t>
+          <t>Custom Gaming / Workstation PC Assembly</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>700</v>
+        <v>1299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Assembling CPU components, cable management, thermal paste application, and stress testing.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Custom Gaming / Workstation PC Assembly procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{"text": "Expert computer &amp; laptop repair service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Computer &amp; Laptop Repair technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Custom Gaming / Workstation PC Assembly procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.764821+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.764821+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does Custom Gaming / Workstation PC Assembly take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
@@ -562,695 +548,765 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair Service Variation 2</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Computer &amp; Device Support</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair</t>
+          <t>Data Recovery from Crashed Hard Drive / SSD</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>900</v>
+        <v>1499</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Deep sector scan recovering lost family photos, business documents, and corrupted partitions.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Data Recovery from Crashed Hard Drive / SSD procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{"text": "Expert computer &amp; laptop repair service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Computer &amp; Laptop Repair technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Data Recovery from Crashed Hard Drive / SSD procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.768904+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.768904+00:00</t>
+          <t>[{'answer': 'The session typically takes around 120 minutes.', 'question': 'How long does Data Recovery from Crashed Hard Drive / SSD take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>d4120b99-4c26-5694-aa19-a6171a3b8d76</t>
+          <t>0cc0099f-92a7-59dc-a33e-81ff8283e62a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair Service Variation 3</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Computer &amp; Device Support</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair</t>
+          <t>Laptop Hardware Repair &amp; Screen Replacement</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1100</v>
+        <v>999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Diagnostic inspection, broken LED screen change, keyboard replacement, or hinge repair.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Laptop Hardware Repair &amp; Screen Replacement procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{"text": "Expert computer &amp; laptop repair service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Computer &amp; Laptop Repair technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Laptop Hardware Repair &amp; Screen Replacement procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.771227+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.771227+00:00</t>
+          <t>[{'answer': 'The session typically takes around 90 minutes.', 'question': 'How long does Laptop Hardware Repair &amp; Screen Replacement take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bb262203-787d-5327-855d-bf954a8ee5d5</t>
+          <t>47f7bb44-468b-5f4f-8984-16fdd6060fa5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair Service Variation 4</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Computer &amp; Device Support</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair</t>
+          <t>Printer Installation &amp; Wireless Network Sharing</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1300</v>
+        <v>399</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Installing wireless ink-tank printer drivers and enabling mobile printing across family devices.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Printer Installation &amp; Wireless Network Sharing procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[{"text": "Expert computer &amp; laptop repair service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Computer &amp; Laptop Repair technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Printer Installation &amp; Wireless Network Sharing procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.773667+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.773667+00:00</t>
+          <t>[{'answer': 'The session typically takes around 30 minutes.', 'question': 'How long does Printer Installation &amp; Wireless Network Sharing take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>65d7ab71-f770-5dd9-a583-b838ec13072f</t>
+          <t>362ba679-8a20-599c-9909-fea400931454</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair Service Variation 5</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Computer &amp; Device Support</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair</t>
+          <t>Virus &amp; Malware Removal Deep Clean</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1500</v>
+        <v>499</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Removing browser hijackers, ransomware threats, and installing genuine antivirus software.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Virus &amp; Malware Removal Deep Clean procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{"text": "Expert computer &amp; laptop repair service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Computer &amp; Laptop Repair technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Virus &amp; Malware Removal Deep Clean procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.776327+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.776327+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Virus &amp; Malware Removal Deep Clean take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2e15793f-1ce5-5cda-88eb-72fb5eedece4</t>
+          <t>05d26f2b-3da7-5cfb-af51-6b35564d00a5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair Service Variation 6</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Computer &amp; Device Support</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair</t>
+          <t>Windows / Mac OS Format &amp; Reinstallation</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1700</v>
+        <v>699</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Clean OS installation, official driver updates, software setup, and data backup transfer.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Windows / Mac OS Format &amp; Reinstallation procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{"text": "Expert computer &amp; laptop repair service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Computer &amp; Laptop Repair technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Windows / Mac OS Format &amp; Reinstallation procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.779343+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.779343+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Windows / Mac OS Format &amp; Reinstallation take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>362ba679-8a20-599c-9909-fea400931454</t>
+          <t>bb262203-787d-5327-855d-bf954a8ee5d5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair Service Variation 7</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Computer &amp; Laptop Repair</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair</t>
+          <t>Computer &amp; Laptop Repair Premium Care Option 11</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1900</v>
+        <v>3099</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Computer &amp; Laptop Repair service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Computer &amp; Laptop Repair Premium Care Option 11 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{"text": "Expert computer &amp; laptop repair service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Computer &amp; Laptop Repair technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Computer &amp; Laptop Repair Premium Care Option 11 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.781718+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.781718+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Computer &amp; Laptop Repair Premium Care Option 11 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8a10f3bf-924a-5055-adae-e72085096ab2</t>
+          <t>d4120b99-4c26-5694-aa19-a6171a3b8d76</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup Service Variation 1</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Computer &amp; Laptop Repair</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup</t>
+          <t>Computer &amp; Laptop Repair Premium Care Option 13</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>700</v>
+        <v>3299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Computer &amp; Laptop Repair service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Computer &amp; Laptop Repair Premium Care Option 13 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{"text": "Expert data recovery &amp; backup service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Data Recovery &amp; Backup technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Computer &amp; Laptop Repair Premium Care Option 13 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.783822+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.783822+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Computer &amp; Laptop Repair Premium Care Option 13 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ba47745f-471d-5556-9527-5da8766dd06a</t>
+          <t>d4e6bfe2-ecbd-5815-b7c7-05784074772a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup Service Variation 2</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Computer &amp; Laptop Repair</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup</t>
+          <t>Computer &amp; Laptop Repair Premium Care Option 14</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>900</v>
+        <v>3399</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Computer &amp; Laptop Repair service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Computer &amp; Laptop Repair Premium Care Option 14 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[{"text": "Expert data recovery &amp; backup service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Data Recovery &amp; Backup technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Computer &amp; Laptop Repair Premium Care Option 14 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.786285+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.786285+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Computer &amp; Laptop Repair Premium Care Option 14 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6e0e4e89-7e40-5b24-a612-9c6a0e00882b</t>
+          <t>65d7ab71-f770-5dd9-a583-b838ec13072f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup Service Variation 3</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Computer &amp; Laptop Repair</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup</t>
+          <t>Computer &amp; Laptop Repair Premium Care Option 3</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1100</v>
+        <v>2299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Computer &amp; Laptop Repair service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Computer &amp; Laptop Repair Premium Care Option 3 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[{"text": "Expert data recovery &amp; backup service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Data Recovery &amp; Backup technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Computer &amp; Laptop Repair Premium Care Option 3 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.789171+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.789171+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Computer &amp; Laptop Repair Premium Care Option 3 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>e3889f5d-53dc-5e48-9e11-c141306cddbb</t>
+          <t>ba47745f-471d-5556-9527-5da8766dd06a</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup Service Variation 4</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Data Recovery &amp; Backup</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup</t>
+          <t>Data Recovery &amp; Backup Premium Care Option 10</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1300</v>
+        <v>2999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Data Recovery &amp; Backup service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Data Recovery &amp; Backup Premium Care Option 10 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[{"text": "Expert data recovery &amp; backup service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Data Recovery &amp; Backup technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Data Recovery &amp; Backup Premium Care Option 10 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.791345+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.791345+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Data Recovery &amp; Backup Premium Care Option 10 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>f2053a99-60b4-58a3-95df-a5fa5c45b87b</t>
+          <t>e3889f5d-53dc-5e48-9e11-c141306cddbb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup Service Variation 5</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Data Recovery &amp; Backup</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup</t>
+          <t>Data Recovery &amp; Backup Premium Care Option 17</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1500</v>
+        <v>3699</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Data Recovery &amp; Backup service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Data Recovery &amp; Backup Premium Care Option 17 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[{"text": "Expert data recovery &amp; backup service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Data Recovery &amp; Backup technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Data Recovery &amp; Backup Premium Care Option 17 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.793851+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.793851+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Data Recovery &amp; Backup Premium Care Option 17 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>f3e717c6-4827-565b-a518-7ac71d1ea8eb</t>
+          <t>f2053a99-60b4-58a3-95df-a5fa5c45b87b</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation Service Variation 1</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Data Recovery &amp; Backup</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation</t>
+          <t>Data Recovery &amp; Backup Premium Care Option 21</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>700</v>
+        <v>4099</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Data Recovery &amp; Backup service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Data Recovery &amp; Backup Premium Care Option 21 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[{"text": "Expert it support &amp; consultation service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified IT Support &amp; Consultation technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Data Recovery &amp; Backup Premium Care Option 21 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.796756+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.796756+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Data Recovery &amp; Backup Premium Care Option 21 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>e4a6bbad-6390-5fae-a8fb-15913428ab91</t>
+          <t>6e0e4e89-7e40-5b24-a612-9c6a0e00882b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation Service Variation 2</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Data Recovery &amp; Backup</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation</t>
+          <t>Data Recovery &amp; Backup Premium Care Option 4</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>900</v>
+        <v>2399</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Data Recovery &amp; Backup service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Data Recovery &amp; Backup Premium Care Option 4 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{"text": "Expert it support &amp; consultation service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified IT Support &amp; Consultation technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Data Recovery &amp; Backup Premium Care Option 4 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.799021+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.799021+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Data Recovery &amp; Backup Premium Care Option 4 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>47f7bb44-468b-5f4f-8984-16fdd6060fa5</t>
+          <t>8a10f3bf-924a-5055-adae-e72085096ab2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation Service Variation 3</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Data Recovery &amp; Backup</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation</t>
+          <t>Data Recovery &amp; Backup Premium Care Option 9</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1100</v>
+        <v>2899</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Data Recovery &amp; Backup service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Data Recovery &amp; Backup Premium Care Option 9 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{"text": "Expert it support &amp; consultation service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified IT Support &amp; Consultation technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Data Recovery &amp; Backup Premium Care Option 9 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.801443+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.801443+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Data Recovery &amp; Backup Premium Care Option 9 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
@@ -1262,645 +1318,710 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation Service Variation 4</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>IT Support &amp; Consultation</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation</t>
+          <t>IT Support &amp; Consultation Premium Care Option 1</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1300</v>
+        <v>2099</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end IT Support &amp; Consultation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional IT Support &amp; Consultation Premium Care Option 1 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[{"text": "Expert it support &amp; consultation service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified IT Support &amp; Consultation technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete IT Support &amp; Consultation Premium Care Option 1 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.803632+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.803632+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does IT Support &amp; Consultation Premium Care Option 1 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5eb558af-feb7-5a9b-ab1a-f277c4c732f9</t>
+          <t>e3a9c71b-d11a-59b2-b916-8b46ce0870e0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation Service Variation 5</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>IT Support &amp; Consultation</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation</t>
+          <t>IT Support &amp; Consultation Premium Care Option 18</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1500</v>
+        <v>3799</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end IT Support &amp; Consultation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional IT Support &amp; Consultation Premium Care Option 18 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{"text": "Expert it support &amp; consultation service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified IT Support &amp; Consultation technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete IT Support &amp; Consultation Premium Care Option 18 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.805790+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.805790+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does IT Support &amp; Consultation Premium Care Option 18 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1b08e54b-37bb-5a80-b491-60c37e610ce9</t>
+          <t>e4a6bbad-6390-5fae-a8fb-15913428ab91</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation Service Variation 6</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>IT Support &amp; Consultation</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation</t>
+          <t>IT Support &amp; Consultation Premium Care Option 19</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1700</v>
+        <v>3899</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end IT Support &amp; Consultation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional IT Support &amp; Consultation Premium Care Option 19 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{"text": "Expert it support &amp; consultation service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified IT Support &amp; Consultation technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete IT Support &amp; Consultation Premium Care Option 19 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.808491+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.808491+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does IT Support &amp; Consultation Premium Care Option 19 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>e3a9c71b-d11a-59b2-b916-8b46ce0870e0</t>
+          <t>5eb558af-feb7-5a9b-ab1a-f277c4c732f9</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation Service Variation 7</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>IT Support &amp; Consultation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation</t>
+          <t>IT Support &amp; Consultation Premium Care Option 2</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1900</v>
+        <v>2199</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end IT Support &amp; Consultation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional IT Support &amp; Consultation Premium Care Option 2 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{"text": "Expert it support &amp; consultation service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified IT Support &amp; Consultation technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete IT Support &amp; Consultation Premium Care Option 2 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.811425+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.811425+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does IT Support &amp; Consultation Premium Care Option 2 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>f1db2450-531c-5da1-8112-1c9b9dc1075d</t>
+          <t>f3e717c6-4827-565b-a518-7ac71d1ea8eb</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Networking &amp; Wi-Fi Setup Service Variation 1</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>IT Support &amp; Consultation</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Networking &amp; Wi-Fi Setup</t>
+          <t>IT Support &amp; Consultation Premium Care Option 22</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>700</v>
+        <v>4199</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end IT Support &amp; Consultation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional IT Support &amp; Consultation Premium Care Option 22 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{"text": "Expert networking &amp; wi-fi setup service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Networking &amp; Wi-Fi Setup technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete IT Support &amp; Consultation Premium Care Option 22 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.813883+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.813883+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does IT Support &amp; Consultation Premium Care Option 22 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7713cd40-cf0b-5696-980e-cd4ab4811d84</t>
+          <t>dc0118a0-ca7c-583c-a62b-c4cdaa25f9d0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Networking &amp; Wi-Fi Setup Service Variation 2</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Networking &amp; Wi-Fi Setup</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Networking &amp; Wi-Fi Setup</t>
+          <t>Networking &amp; Wi-Fi Setup Premium Care Option 15</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>900</v>
+        <v>3499</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Networking &amp; Wi-Fi Setup service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Networking &amp; Wi-Fi Setup Premium Care Option 15 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{"text": "Expert networking &amp; wi-fi setup service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Networking &amp; Wi-Fi Setup technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Networking &amp; Wi-Fi Setup Premium Care Option 15 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.817303+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.817303+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Networking &amp; Wi-Fi Setup Premium Care Option 15 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>729fe3fb-75bf-563d-88c8-2eee1ca749b1</t>
+          <t>f1db2450-531c-5da1-8112-1c9b9dc1075d</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Networking &amp; Wi-Fi Setup Service Variation 3</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Networking &amp; Wi-Fi Setup</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Networking &amp; Wi-Fi Setup</t>
+          <t>Networking &amp; Wi-Fi Setup Premium Care Option 20</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1100</v>
+        <v>3999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Networking &amp; Wi-Fi Setup service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Networking &amp; Wi-Fi Setup Premium Care Option 20 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{"text": "Expert networking &amp; wi-fi setup service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Networking &amp; Wi-Fi Setup technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Networking &amp; Wi-Fi Setup Premium Care Option 20 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.819609+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.819609+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Networking &amp; Wi-Fi Setup Premium Care Option 20 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0cc0099f-92a7-59dc-a33e-81ff8283e62a</t>
+          <t>729fe3fb-75bf-563d-88c8-2eee1ca749b1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Networking &amp; Wi-Fi Setup Service Variation 4</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Networking &amp; Wi-Fi Setup</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Networking &amp; Wi-Fi Setup</t>
+          <t>Networking &amp; Wi-Fi Setup Premium Care Option 6</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1300</v>
+        <v>2599</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Networking &amp; Wi-Fi Setup service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Networking &amp; Wi-Fi Setup Premium Care Option 6 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[{"text": "Expert networking &amp; wi-fi setup service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Networking &amp; Wi-Fi Setup technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Networking &amp; Wi-Fi Setup Premium Care Option 6 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.821938+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.821938+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Networking &amp; Wi-Fi Setup Premium Care Option 6 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dc0118a0-ca7c-583c-a62b-c4cdaa25f9d0</t>
+          <t>7713cd40-cf0b-5696-980e-cd4ab4811d84</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Networking &amp; Wi-Fi Setup Service Variation 5</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Networking &amp; Wi-Fi Setup</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Networking &amp; Wi-Fi Setup</t>
+          <t>Networking &amp; Wi-Fi Setup Premium Care Option 7</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1500</v>
+        <v>2699</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Networking &amp; Wi-Fi Setup service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Networking &amp; Wi-Fi Setup Premium Care Option 7 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[{"text": "Expert networking &amp; wi-fi setup service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Networking &amp; Wi-Fi Setup technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Networking &amp; Wi-Fi Setup Premium Care Option 7 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.824112+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.824112+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Networking &amp; Wi-Fi Setup Premium Care Option 7 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>d0141ca3-4157-5374-b1bc-35b8cf628d97</t>
+          <t>37282030-df16-538a-b975-ab6d804922ba</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Website &amp; App Development Service Variation 1</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Network &amp; Smart Devices</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Website &amp; App Development</t>
+          <t>Smart TV &amp; Soundbar Home Theater Integration</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>HDMI eARC audio wiring, Bluetooth speaker pairing, and streaming app subscription login.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Smart TV &amp; Soundbar Home Theater Integration procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[{"text": "Expert website &amp; app development service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Website &amp; App Development technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Smart TV &amp; Soundbar Home Theater Integration procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.826376+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.826376+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Smart TV &amp; Soundbar Home Theater Integration take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05d26f2b-3da7-5cfb-af51-6b35564d00a5</t>
+          <t>1b08e54b-37bb-5a80-b491-60c37e610ce9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Website &amp; App Development Service Variation 2</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Network &amp; Smart Devices</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Website &amp; App Development</t>
+          <t>Wi-Fi Router Setup &amp; Mesh Network Expansion</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>900</v>
+        <v>499</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Configuring dual-band Wi-Fi router, dead-zone troubleshooting, and password security setup.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Wi-Fi Router Setup &amp; Mesh Network Expansion procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[{"text": "Expert website &amp; app development service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Website &amp; App Development technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Wi-Fi Router Setup &amp; Mesh Network Expansion procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.829279+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.829279+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Wi-Fi Router Setup &amp; Mesh Network Expansion take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ddf9ec41-154d-5e26-a0d3-2cb544e9fd5b</t>
+          <t>d0141ca3-4157-5374-b1bc-35b8cf628d97</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Website &amp; App Development Service Variation 3</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Website &amp; App Development</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Website &amp; App Development</t>
+          <t>Website &amp; App Development Premium Care Option 12</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1100</v>
+        <v>3199</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Website &amp; App Development service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Website &amp; App Development Premium Care Option 12 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[{"text": "Expert website &amp; app development service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Website &amp; App Development technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Website &amp; App Development Premium Care Option 12 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.831552+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.831552+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Website &amp; App Development Premium Care Option 12 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>37282030-df16-538a-b975-ab6d804922ba</t>
+          <t>ddf9ec41-154d-5e26-a0d3-2cb544e9fd5b</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Website &amp; App Development Service Variation 4</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Website &amp; App Development</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Website &amp; App Development</t>
+          <t>Website &amp; App Development Premium Care Option 16</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1300</v>
+        <v>3599</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Website &amp; App Development service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Website &amp; App Development Premium Care Option 16 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[{"text": "Expert website &amp; app development service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Website &amp; App Development technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Website &amp; App Development Premium Care Option 16 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.834175+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.834175+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Website &amp; App Development Premium Care Option 16 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
@@ -1912,45 +2033,50 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Website &amp; App Development Service Variation 5</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Website &amp; App Development</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Website &amp; App Development</t>
+          <t>Website &amp; App Development Premium Care Option 5</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1500</v>
+        <v>2499</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Website &amp; App Development service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Website &amp; App Development Premium Care Option 5 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[{"text": "Expert website &amp; app development service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Website &amp; App Development technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Website &amp; App Development Premium Care Option 5 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.836509+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.836509+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Website &amp; App Development Premium Care Option 5 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
@@ -1962,45 +2088,50 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Website &amp; App Development Service Variation 6</t>
+          <t>12. Technology &amp; Digital Services</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>12. Technology &amp; Digital Services</t>
+          <t>Website &amp; App Development</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Website &amp; App Development</t>
+          <t>Website &amp; App Development Premium Care Option 8</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1700</v>
+        <v>2799</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Website &amp; App Development service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>["Remote or on-site diagnosis", "Service execution and testing", "30-day follow-up support", "Basic user training"]</t>
+          <t>['Professional Website &amp; App Development Premium Care Option 8 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[{"text": "Expert website &amp; app development service to resolve your technology challenges swiftly.", "type": "description"}, {"type": "highlights", "items": ["Certified Website &amp; App Development technician", "On-site and remote support available", "No fix, no charge policy", "Data safety guaranteed"]}, {"type": "excluded_scope", "items": ["Cost of replacement hardware or parts", "Software licensing fees"]}, {"type": "process_steps", "steps": [{"title": "Diagnosis", "description": "Identifying the root cause of the technical issue", "step_number": 1}, {"title": "Solution Planning", "description": "Outlining the fix or upgrade path", "step_number": 2}, {"title": "Service Execution", "description": "Carrying out repairs, setup, or development work", "step_number": 3}, {"title": "Testing &amp; Verification", "description": "Confirming the solution works correctly", "step_number": 4}, {"title": "User Handover", "description": "Demonstrating the fix and advising on best practices", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Keep OS and software updated regularly", "Use a UPS to prevent power surge damage"]}, {"type": "tools_materials", "tools": ["Diagnostic software", "Screwdriver kit", "Anti-static tools", "Network analyser"], "materials": []}, {"type": "customer_setup", "requirements": ["Back up important data before the visit", "Ensure stable power supply", "Provide access to router/modem if networking issue"]}, {"type": "expected_results", "items": "A fully functional device with improved performance and security."}, {"type": "important_notes", "items": "Data loss due to hardware failure is not covered unless data recovery service is booked."}, {"type": "warranty", "details": "30-day service warranty on all repairs; free revisit if same issue reoccurs.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "Yes, many issues can be resolved remotely via secure screen-sharing.", "question": "Do you offer remote support?"}, {"answer": "We follow a no-fix, no-charge policy for diagnosis visits.", "question": "What if the problem cannot be fixed?"}, {"answer": "Yes, our technicians follow strict data privacy protocols.", "question": "Are my data and privacy safe?"}, {"answer": "Yes, we service all major brands — Apple, Dell, HP, Lenovo, and more.", "question": "Do you repair all brands?"}]}, {"type": "tips", "items": ["Always back up your data weekly to avoid permanent loss."]}, {"dos": ["Describe error messages or symptoms clearly to speed up diagnosis."], "type": "dos_donts", "donts": ["Do not attempt DIY fixes before the technician arrives — it may void the warranty."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Website &amp; App Development Premium Care Option 8 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.838700+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.838700+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Website &amp; App Development Premium Care Option 8 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>

--- a/backend/backups/category12_technology_digital_services_FINAL.xlsx
+++ b/backend/backups/category12_technology_digital_services_FINAL.xlsx
@@ -818,7 +818,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bb262203-787d-5327-855d-bf954a8ee5d5</t>
+          <t>d4120b99-4c26-5694-aa19-a6171a3b8d76</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -833,47 +833,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair Premium Care Option 11</t>
+          <t>Broken Laptop Hinge &amp; Casing Fabrication</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3099</v>
+        <v>1199</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Specialized high-end Computer &amp; Laptop Repair service tailored to specific client needs with extended guarantee.</t>
+          <t>Industrial epoxy rebonding or replacing cracked plastic top casing and tight hinges.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>['Professional Computer &amp; Laptop Repair Premium Care Option 11 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Broken Laptop Hinge &amp; Casing Fabrication procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>['Complete Computer &amp; Laptop Repair Premium Care Option 11 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Broken Laptop Hinge &amp; Casing Fabrication procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Computer &amp; Laptop Repair Premium Care Option 11 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 90 minutes.', 'question': 'How long does Broken Laptop Hinge &amp; Casing Fabrication take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>d4120b99-4c26-5694-aa19-a6171a3b8d76</t>
+          <t>d4e6bfe2-ecbd-5815-b7c7-05784074772a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -888,47 +888,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair Premium Care Option 13</t>
+          <t>Motherboard Micro-Soldering &amp; Chipset Repair</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3299</v>
+        <v>1799</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Specialized high-end Computer &amp; Laptop Repair service tailored to specific client needs with extended guarantee.</t>
+          <t>BGA chip rework, short circuit mosfet replacement, and power IC diagnostics.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>['Professional Computer &amp; Laptop Repair Premium Care Option 13 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Motherboard Micro-Soldering &amp; Chipset Repair procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>['Complete Computer &amp; Laptop Repair Premium Care Option 13 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Motherboard Micro-Soldering &amp; Chipset Repair procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Computer &amp; Laptop Repair Premium Care Option 13 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 120 minutes.', 'question': 'How long does Motherboard Micro-Soldering &amp; Chipset Repair take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>d4e6bfe2-ecbd-5815-b7c7-05784074772a</t>
+          <t>bb262203-787d-5327-855d-bf954a8ee5d5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -943,40 +943,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair Premium Care Option 14</t>
+          <t>SSD Upgrade &amp; Cloning (Without Data Loss)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3399</v>
+        <v>799</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Specialized high-end Computer &amp; Laptop Repair service tailored to specific client needs with extended guarantee.</t>
+          <t>Replacing slow mechanical hard drives with high-speed NVMe/SATA SSD with full OS cloning.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>['Professional Computer &amp; Laptop Repair Premium Care Option 14 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional SSD Upgrade &amp; Cloning (Without Data Loss) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>['Complete Computer &amp; Laptop Repair Premium Care Option 14 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete SSD Upgrade &amp; Cloning (Without Data Loss) procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Computer &amp; Laptop Repair Premium Care Option 14 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does SSD Upgrade &amp; Cloning (Without Data Loss) take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -998,47 +998,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Computer &amp; Laptop Repair Premium Care Option 3</t>
+          <t>Thermal Paste Replacement &amp; Cooling Fan Clean</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2299</v>
+        <v>599</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Specialized high-end Computer &amp; Laptop Repair service tailored to specific client needs with extended guarantee.</t>
+          <t>Arctic MX-4 thermal compound application stopping laptop overheating and thermal throttling.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>['Professional Computer &amp; Laptop Repair Premium Care Option 3 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Thermal Paste Replacement &amp; Cooling Fan Clean procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>['Complete Computer &amp; Laptop Repair Premium Care Option 3 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Thermal Paste Replacement &amp; Cooling Fan Clean procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Computer &amp; Laptop Repair Premium Care Option 3 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Thermal Paste Replacement &amp; Cooling Fan Clean take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ba47745f-471d-5556-9527-5da8766dd06a</t>
+          <t>6e0e4e89-7e40-5b24-a612-9c6a0e00882b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1053,47 +1053,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup Premium Care Option 10</t>
+          <t>Accidentally Formatted Pen Drive / SD Card Recovery</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2999</v>
+        <v>899</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Specialized high-end Data Recovery &amp; Backup service tailored to specific client needs with extended guarantee.</t>
+          <t>Deep file carve scanning restoring deleted family photos, videos, and zip archives.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>['Professional Data Recovery &amp; Backup Premium Care Option 10 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Accidentally Formatted Pen Drive / SD Card Recovery procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>['Complete Data Recovery &amp; Backup Premium Care Option 10 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Accidentally Formatted Pen Drive / SD Card Recovery procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Data Recovery &amp; Backup Premium Care Option 10 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Accidentally Formatted Pen Drive / SD Card Recovery take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>e3889f5d-53dc-5e48-9e11-c141306cddbb</t>
+          <t>ba47745f-471d-5556-9527-5da8766dd06a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1108,47 +1108,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup Premium Care Option 17</t>
+          <t>Automated Cloud Backup Setup (Google Drive/OneDrive)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3699</v>
+        <v>499</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Specialized high-end Data Recovery &amp; Backup service tailored to specific client needs with extended guarantee.</t>
+          <t>Configuring scheduled real-time synchronization of desktop folders to secure cloud.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>['Professional Data Recovery &amp; Backup Premium Care Option 17 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Automated Cloud Backup Setup (Google Drive/OneDrive) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>['Complete Data Recovery &amp; Backup Premium Care Option 17 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Automated Cloud Backup Setup (Google Drive/OneDrive) procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Data Recovery &amp; Backup Premium Care Option 17 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 40 minutes.', 'question': 'How long does Automated Cloud Backup Setup (Google Drive/OneDrive) take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>f2053a99-60b4-58a3-95df-a5fa5c45b87b</t>
+          <t>8a10f3bf-924a-5055-adae-e72085096ab2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1163,47 +1163,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup Premium Care Option 21</t>
+          <t>Corrupted External Hard Drive File Retrieval</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4099</v>
+        <v>1499</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Specialized high-end Data Recovery &amp; Backup service tailored to specific client needs with extended guarantee.</t>
+          <t>Fixing RAW filesystem errors and retrieving lost partition documents.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>['Professional Data Recovery &amp; Backup Premium Care Option 21 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Corrupted External Hard Drive File Retrieval procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>['Complete Data Recovery &amp; Backup Premium Care Option 21 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Corrupted External Hard Drive File Retrieval procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Data Recovery &amp; Backup Premium Care Option 21 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 120 minutes.', 'question': 'How long does Corrupted External Hard Drive File Retrieval take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6e0e4e89-7e40-5b24-a612-9c6a0e00882b</t>
+          <t>e3889f5d-53dc-5e48-9e11-c141306cddbb</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1218,47 +1218,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup Premium Care Option 4</t>
+          <t>Ransomware Encrypted File Analysis &amp; Recovery</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2399</v>
+        <v>2499</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Specialized high-end Data Recovery &amp; Backup service tailored to specific client needs with extended guarantee.</t>
+          <t>Decryption tool analysis, shadow copy extraction, and system clean sanitization.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>['Professional Data Recovery &amp; Backup Premium Care Option 4 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Ransomware Encrypted File Analysis &amp; Recovery procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>['Complete Data Recovery &amp; Backup Premium Care Option 4 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Ransomware Encrypted File Analysis &amp; Recovery procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Data Recovery &amp; Backup Premium Care Option 4 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 180 minutes.', 'question': 'How long does Ransomware Encrypted File Analysis &amp; Recovery take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8a10f3bf-924a-5055-adae-e72085096ab2</t>
+          <t>f2053a99-60b4-58a3-95df-a5fa5c45b87b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1273,47 +1273,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Data Recovery &amp; Backup Premium Care Option 9</t>
+          <t>Smartphone Dead Screen Data Extraction</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2899</v>
+        <v>1199</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Specialized high-end Data Recovery &amp; Backup service tailored to specific client needs with extended guarantee.</t>
+          <t>Connecting OTG debugging interface to extract WhatsApp chats, contacts, and photos from broken phone.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>['Professional Data Recovery &amp; Backup Premium Care Option 9 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Smartphone Dead Screen Data Extraction procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>['Complete Data Recovery &amp; Backup Premium Care Option 9 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Smartphone Dead Screen Data Extraction procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Data Recovery &amp; Backup Premium Care Option 9 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Smartphone Dead Screen Data Extraction take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5bfb93e1-e97d-58f0-a2fd-773cbbb6f72f</t>
+          <t>5eb558af-feb7-5a9b-ab1a-f277c4c732f9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1328,47 +1328,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation Premium Care Option 1</t>
+          <t>Corporate Email &amp; Google Workspace Domain Migration</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2099</v>
+        <v>1999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Specialized high-end IT Support &amp; Consultation service tailored to specific client needs with extended guarantee.</t>
+          <t>Configuring MX, SPF, DKIM DNS records and migrating mailbox data seamlessly.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>['Professional IT Support &amp; Consultation Premium Care Option 1 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Corporate Email &amp; Google Workspace Domain Migration procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>['Complete IT Support &amp; Consultation Premium Care Option 1 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Corporate Email &amp; Google Workspace Domain Migration procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does IT Support &amp; Consultation Premium Care Option 1 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 90 minutes.', 'question': 'How long does Corporate Email &amp; Google Workspace Domain Migration take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>e3a9c71b-d11a-59b2-b916-8b46ce0870e0</t>
+          <t>5bfb93e1-e97d-58f0-a2fd-773cbbb6f72f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1383,47 +1383,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation Premium Care Option 18</t>
+          <t>Home Office Dual-Monitor &amp; Docking Station Setup</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3799</v>
+        <v>699</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Specialized high-end IT Support &amp; Consultation service tailored to specific client needs with extended guarantee.</t>
+          <t>DisplayPort/HDMI daisy chaining, USB-C thunderbolt hub setup, and ergonomic cable routing.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>['Professional IT Support &amp; Consultation Premium Care Option 18 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Home Office Dual-Monitor &amp; Docking Station Setup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>['Complete IT Support &amp; Consultation Premium Care Option 18 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Home Office Dual-Monitor &amp; Docking Station Setup procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does IT Support &amp; Consultation Premium Care Option 18 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Home Office Dual-Monitor &amp; Docking Station Setup take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>e4a6bbad-6390-5fae-a8fb-15913428ab91</t>
+          <t>f3e717c6-4827-565b-a518-7ac71d1ea8eb</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1438,47 +1438,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation Premium Care Option 19</t>
+          <t>Point of Sale (POS) Billing Software Configuration</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3899</v>
+        <v>1499</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Specialized high-end IT Support &amp; Consultation service tailored to specific client needs with extended guarantee.</t>
+          <t>Installing thermal receipt printers, barcode scanners, and inventory billing software.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>['Professional IT Support &amp; Consultation Premium Care Option 19 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Point of Sale (POS) Billing Software Configuration procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>['Complete IT Support &amp; Consultation Premium Care Option 19 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Point of Sale (POS) Billing Software Configuration procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does IT Support &amp; Consultation Premium Care Option 19 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 90 minutes.', 'question': 'How long does Point of Sale (POS) Billing Software Configuration take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5eb558af-feb7-5a9b-ab1a-f277c4c732f9</t>
+          <t>e3a9c71b-d11a-59b2-b916-8b46ce0870e0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1493,47 +1493,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation Premium Care Option 2</t>
+          <t>Small Office Network Attached Storage (NAS) Setup</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2199</v>
+        <v>2499</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Specialized high-end IT Support &amp; Consultation service tailored to specific client needs with extended guarantee.</t>
+          <t>Synology/QNAP raid storage configuration with multi-user permissions and remote access.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>['Professional IT Support &amp; Consultation Premium Care Option 2 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Small Office Network Attached Storage (NAS) Setup procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>['Complete IT Support &amp; Consultation Premium Care Option 2 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Small Office Network Attached Storage (NAS) Setup procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does IT Support &amp; Consultation Premium Care Option 2 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 120 minutes.', 'question': 'How long does Small Office Network Attached Storage (NAS) Setup take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>f3e717c6-4827-565b-a518-7ac71d1ea8eb</t>
+          <t>e4a6bbad-6390-5fae-a8fb-15913428ab91</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1548,47 +1548,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IT Support &amp; Consultation Premium Care Option 22</t>
+          <t>Software License Audit &amp; Cybersecurity Scan</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4199</v>
+        <v>1299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Specialized high-end IT Support &amp; Consultation service tailored to specific client needs with extended guarantee.</t>
+          <t>Scanning network vulnerabilities, updating firewall rules, and verifying license compliance.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>['Professional IT Support &amp; Consultation Premium Care Option 22 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Software License Audit &amp; Cybersecurity Scan procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>['Complete IT Support &amp; Consultation Premium Care Option 22 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Software License Audit &amp; Cybersecurity Scan procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does IT Support &amp; Consultation Premium Care Option 22 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Software License Audit &amp; Cybersecurity Scan take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>dc0118a0-ca7c-583c-a62b-c4cdaa25f9d0</t>
+          <t>7713cd40-cf0b-5696-980e-cd4ab4811d84</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1603,47 +1603,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Networking &amp; Wi-Fi Setup Premium Care Option 15</t>
+          <t>Ethernet Cable Crimping &amp; Concealed Wall Punching</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3499</v>
+        <v>699</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Specialized high-end Networking &amp; Wi-Fi Setup service tailored to specific client needs with extended guarantee.</t>
+          <t>Cat6 gigabit cable termination with RJ45 connectors and wall faceplate keystones.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>['Professional Networking &amp; Wi-Fi Setup Premium Care Option 15 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Ethernet Cable Crimping &amp; Concealed Wall Punching procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>['Complete Networking &amp; Wi-Fi Setup Premium Care Option 15 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Ethernet Cable Crimping &amp; Concealed Wall Punching procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Networking &amp; Wi-Fi Setup Premium Care Option 15 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Ethernet Cable Crimping &amp; Concealed Wall Punching take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>f1db2450-531c-5da1-8112-1c9b9dc1075d</t>
+          <t>dc0118a0-ca7c-583c-a62b-c4cdaa25f9d0</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1658,40 +1658,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Networking &amp; Wi-Fi Setup Premium Care Option 20</t>
+          <t>Fiber Broadband ONT Modem Configuration</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3999</v>
+        <v>499</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Specialized high-end Networking &amp; Wi-Fi Setup service tailored to specific client needs with extended guarantee.</t>
+          <t>Configuring PPPoE credentials, static IP assignment, and 5GHz band channel optimization.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>['Professional Networking &amp; Wi-Fi Setup Premium Care Option 20 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Fiber Broadband ONT Modem Configuration procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>['Complete Networking &amp; Wi-Fi Setup Premium Care Option 20 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Fiber Broadband ONT Modem Configuration procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Networking &amp; Wi-Fi Setup Premium Care Option 20 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 30 minutes.', 'question': 'How long does Fiber Broadband ONT Modem Configuration take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1713,47 +1713,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Networking &amp; Wi-Fi Setup Premium Care Option 6</t>
+          <t>Multi-Story Tri-Band Mesh Wi-Fi Installation</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2599</v>
+        <v>899</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Specialized high-end Networking &amp; Wi-Fi Setup service tailored to specific client needs with extended guarantee.</t>
+          <t>Eliminating dead zones in large homes using seamless roaming Deco/Orbi mesh nodes.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>['Professional Networking &amp; Wi-Fi Setup Premium Care Option 6 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Multi-Story Tri-Band Mesh Wi-Fi Installation procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>['Complete Networking &amp; Wi-Fi Setup Premium Care Option 6 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Multi-Story Tri-Band Mesh Wi-Fi Installation procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Networking &amp; Wi-Fi Setup Premium Care Option 6 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Multi-Story Tri-Band Mesh Wi-Fi Installation take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7713cd40-cf0b-5696-980e-cd4ab4811d84</t>
+          <t>f1db2450-531c-5da1-8112-1c9b9dc1075d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1768,40 +1768,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Networking &amp; Wi-Fi Setup Premium Care Option 7</t>
+          <t>Secure Guest Wi-Fi &amp; Bandwidth Limiting Portal</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2699</v>
+        <v>899</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Specialized high-end Networking &amp; Wi-Fi Setup service tailored to specific client needs with extended guarantee.</t>
+          <t>Creating isolated guest Wi-Fi networks with captive portals and bandwidth caps.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>['Professional Networking &amp; Wi-Fi Setup Premium Care Option 7 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Secure Guest Wi-Fi &amp; Bandwidth Limiting Portal procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>['Complete Networking &amp; Wi-Fi Setup Premium Care Option 7 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Secure Guest Wi-Fi &amp; Bandwidth Limiting Portal procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Networking &amp; Wi-Fi Setup Premium Care Option 7 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Secure Guest Wi-Fi &amp; Bandwidth Limiting Portal take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1933,47 +1933,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Website &amp; App Development Premium Care Option 12</t>
+          <t>Custom Landing Page Design for Google Ads</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3199</v>
+        <v>2999</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Specialized high-end Website &amp; App Development service tailored to specific client needs with extended guarantee.</t>
+          <t>High-converting modern UI page with WhatsApp CTA button and fast 1-second load speed.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>['Professional Website &amp; App Development Premium Care Option 12 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Custom Landing Page Design for Google Ads procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>['Complete Website &amp; App Development Premium Care Option 12 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Custom Landing Page Design for Google Ads procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Website &amp; App Development Premium Care Option 12 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 120 minutes.', 'question': 'How long does Custom Landing Page Design for Google Ads take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ddf9ec41-154d-5e26-a0d3-2cb544e9fd5b</t>
+          <t>7774beae-b345-5741-8073-7227f208458b</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1988,47 +1988,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Website &amp; App Development Premium Care Option 16</t>
+          <t>Shopify E-Commerce Store Launch Consultation</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3599</v>
+        <v>5999</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Specialized high-end Website &amp; App Development service tailored to specific client needs with extended guarantee.</t>
+          <t>Product catalog upload, payment gateway integration (Razorpay/Stripe), and shipping rates.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>['Professional Website &amp; App Development Premium Care Option 16 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Shopify E-Commerce Store Launch Consultation procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>['Complete Website &amp; App Development Premium Care Option 16 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Shopify E-Commerce Store Launch Consultation procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Website &amp; App Development Premium Care Option 16 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 240 minutes.', 'question': 'How long does Shopify E-Commerce Store Launch Consultation take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>70cb57da-cd6e-54bc-903a-42181fa00ef6</t>
+          <t>ddf9ec41-154d-5e26-a0d3-2cb544e9fd5b</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2043,47 +2043,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Website &amp; App Development Premium Care Option 5</t>
+          <t>Website Speed Optimization &amp; Core Web Vitals Fix</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2499</v>
+        <v>1999</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Specialized high-end Website &amp; App Development service tailored to specific client needs with extended guarantee.</t>
+          <t>Minifying CSS/JS, converting WebP images, and achieving 90+ score on Google PageSpeed.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>['Professional Website &amp; App Development Premium Care Option 5 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Website Speed Optimization &amp; Core Web Vitals Fix procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>['Complete Website &amp; App Development Premium Care Option 5 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Website Speed Optimization &amp; Core Web Vitals Fix procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Website &amp; App Development Premium Care Option 5 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 90 minutes.', 'question': 'How long does Website Speed Optimization &amp; Core Web Vitals Fix take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7774beae-b345-5741-8073-7227f208458b</t>
+          <t>70cb57da-cd6e-54bc-903a-42181fa00ef6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2098,40 +2098,40 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Website &amp; App Development Premium Care Option 8</t>
+          <t>WordPress Business Website Setup &amp; Customization</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2799</v>
+        <v>4999</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Specialized high-end Website &amp; App Development service tailored to specific client needs with extended guarantee.</t>
+          <t>Responsive 5-page mobile-friendly website with contact form, SSL certificate, and SEO plugin.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>['Professional Website &amp; App Development Premium Care Option 8 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional WordPress Business Website Setup &amp; Customization procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>['Complete Website &amp; App Development Premium Care Option 8 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete WordPress Business Website Setup &amp; Customization procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Website &amp; App Development Premium Care Option 8 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 240 minutes.', 'question': 'How long does WordPress Business Website Setup &amp; Customization take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
